--- a/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N21_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1912_W0046F0002T0006Z000C1N21_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>11.18505490201549</v>
+        <v>1.817571421577517</v>
       </c>
       <c r="D2" t="n">
-        <v>10.93438961041117</v>
+        <v>1.776838311691816</v>
       </c>
       <c r="E2" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F2" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>11.06225686743547</v>
+        <v>1.797616740958265</v>
       </c>
       <c r="D3" t="n">
-        <v>10.54283615011668</v>
+        <v>1.71321087439396</v>
       </c>
       <c r="E3" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F3" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.54381402447682</v>
+        <v>2.038369778977484</v>
       </c>
       <c r="D4" t="n">
-        <v>24.50465585823877</v>
+        <v>3.982006576963801</v>
       </c>
       <c r="E4" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F4" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>11.22248338188</v>
+        <v>1.8236535495555</v>
       </c>
       <c r="D5" t="n">
-        <v>11.15999049407115</v>
+        <v>1.813498455286562</v>
       </c>
       <c r="E5" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F5" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>7.478488807377409</v>
+        <v>1.215254431198829</v>
       </c>
       <c r="D6" t="n">
-        <v>8.958306606095523</v>
+        <v>1.455724823490522</v>
       </c>
       <c r="E6" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F6" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>18.50916062820206</v>
+        <v>3.007738602082835</v>
       </c>
       <c r="D7" t="n">
-        <v>18.6225574816345</v>
+        <v>3.026165590765606</v>
       </c>
       <c r="E7" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F7" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>7.817040462455963</v>
+        <v>1.270269075149094</v>
       </c>
       <c r="D8" t="n">
-        <v>7.168735822944143</v>
+        <v>1.164919571228423</v>
       </c>
       <c r="E8" t="n">
-        <v>3.386022963671493</v>
+        <v>0.5502287315966178</v>
       </c>
       <c r="F8" t="n">
-        <v>5.705707545024409</v>
+        <v>0.9271774760664665</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
